--- a/human_resources_forms/001_job_satisfaction_survey--human_resources_forms.xlsx
+++ b/human_resources_forms/001_job_satisfaction_survey--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Employee Survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Employee Feedback</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide feedback on your overall job satisfaction.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,62 +547,58 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>job_satisfaction</t>
+          <t>job_satisfaction_scale</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How Satisfied Are You</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Scale from 1 to 5</t>
-        </is>
-      </c>
+          <t>Job Satisfaction</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>manager_support</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Any Feedback</t>
+          <t>Manager Support</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>job_performance</t>
+          <t>manager_communication</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Job Performance</t>
+          <t>Manager Communication</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -611,40 +611,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>job_satisfaction_2</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Overall Satisfaction</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>manager_support</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manager Support</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,17 +657,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>job_satisfaction_3</t>
+          <t>overall_satisfaction</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Job Satisfaction</t>
+          <t>Overall Satisfaction</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,17 +680,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>manager_communication</t>
+          <t>job_satisfaction_level</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How Often Do</t>
+          <t>Job Satisfaction Level</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>communication_frequency</t>
+          <t>contact_number</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Contact Number</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -731,361 +731,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>job_satisfaction_4</t>
+          <t>manager_rating</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Manager Rating</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>job_satisfaction_5</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>job_satisfaction_6</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Job Satisfaction</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>job_satisfaction_7</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Contact Number</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>job_satisfaction_8</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>job_satisfaction_9</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>job_satisfaction_10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>job_satisfaction_11</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>job_satisfaction_12</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>job_satisfaction_13</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>job_satisfaction_14</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>job_satisfaction_15</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,12 +757,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1130,68 +785,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>job_performance_choices</t>
+          <t>manager_support_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>strongly_support</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Strongly Support</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>job_performance_choices</t>
+          <t>manager_support_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>somewhat_support</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Somewhat Support</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>job_performance_choices</t>
+          <t>manager_support_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>job_performance_choices</t>
+          <t>manager_support_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option4':_'poor'}</t>
+          <t>somewhat_neutral</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option4': 'Poor'}</t>
+          <t>Somewhat Neutral</t>
         </is>
       </c>
     </row>
@@ -1203,12 +858,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option1':_'strongly_support'}</t>
+          <t>not_support</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option1': 'Strongly Support'}</t>
+          <t>Not Support</t>
         </is>
       </c>
     </row>
@@ -1220,352 +875,199 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option2':_'somewhat_support'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option2': 'Somewhat Support'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>manager_support_choices</t>
+          <t>manager_communication_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option3':_'neutral'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option3': 'Neutral'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>manager_support_choices</t>
+          <t>manager_communication_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option4':_'somewhat_neutral'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option4': 'Somewhat Neutral'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>manager_support_choices</t>
+          <t>manager_communication_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option5':_'not_support'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option5': 'Not Support'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>manager_support_choices</t>
+          <t>manager_communication_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option6':_'not_at_all'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option6': 'Not at all'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_satisfaction_3_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option1':_'highly_satisfied'}</t>
+          <t>human_resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option1': 'Highly Satisfied'}</t>
+          <t>Human Resources</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_satisfaction_3_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option2':_'satisfied'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option2': 'Satisfied'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_satisfaction_3_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option3':_'neither'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option3': 'Neither'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_satisfaction_3_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option4':_'dissatisfied'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option4': 'Dissatisfied'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_satisfaction_3_choices</t>
+          <t>job_satisfaction_level_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option5':_'very_dissatisfied'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option5': 'Very Dissatisfied'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>manager_communication_choices</t>
+          <t>job_satisfaction_level_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option1':_'often'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option1': 'Often'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>manager_communication_choices</t>
+          <t>job_satisfaction_level_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option2':_'sometimes'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option2': 'Sometimes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>manager_communication_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'option3':_'rarely'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'option3': 'Rarely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>manager_communication_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'option4':_'never'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'option4': 'Never'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>department_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'option1':_'human_resources'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'option1': 'Human Resources'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>department_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'option2':_'marketing'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'option2': 'Marketing'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>department_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'option3':_'sales'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'option3': 'Sales'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>department_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'option4':_'other'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'option4': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>job_satisfaction_6_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'option1':_'high'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'option1': 'High'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>job_satisfaction_6_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'option2':_'medium'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'option2': 'Medium'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>job_satisfaction_6_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'option3':_'low'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'option3': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
